--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-1960" windowWidth="38400" windowHeight="21600" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="Projects" state="visible" r:id="rId4"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="301">
   <si>
     <t>id</t>
   </si>
@@ -47,9 +47,15 @@
     <t>logoPath</t>
   </si>
   <si>
+    <t>contractCurrency</t>
+  </si>
+  <si>
     <t>totalPrice</t>
   </si>
   <si>
+    <t>vatPercent</t>
+  </si>
+  <si>
     <t>totalWithVat</t>
   </si>
   <si>
@@ -92,7 +98,195 @@
     <t>2026-04-07T04:01:46.137Z</t>
   </si>
   <si>
-    <t>2026-04-07T04:02:23.762Z</t>
+    <t>2026-04-26T04:52:45.411Z</t>
+  </si>
+  <si>
+    <t>f34e644b-1284-4be8-9a0a-5479e6462f39</t>
+  </si>
+  <si>
+    <t>GB-00002</t>
+  </si>
+  <si>
+    <t>Exploration Mining</t>
+  </si>
+  <si>
+    <t>Bag, Document envelope</t>
+  </si>
+  <si>
+    <t>2026-04-17</t>
+  </si>
+  <si>
+    <t>Product Name: Document envelope Size: A4 Material: Paper Logo: 1 Position Product Name: Bags Size: 35×25×12 cm Material: canvar A12 Logo: 2 Position</t>
+  </si>
+  <si>
+    <t>/uploads/1775539592788-1773740916417-PHOTO-2026-03-11-17-01-02_2.jpg</t>
+  </si>
+  <si>
+    <t>LAK</t>
+  </si>
+  <si>
+    <t>2026-04-26T08:57:18.382Z</t>
+  </si>
+  <si>
+    <t>aa6538c4-ad60-45ba-94b0-0d31a1bd2ea8</t>
+  </si>
+  <si>
+    <t>GB-00003</t>
+  </si>
+  <si>
+    <t>Tourism Malaysia in Vientiane</t>
+  </si>
+  <si>
+    <t>Bag, Notebook</t>
+  </si>
+  <si>
+    <t>BIN</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>Product Name: Bags Size: 30*43*20cm Material: Linen fabric Logo: 2 Position Product Name: Noted Book Size: 30*43*20cm Material: Paper Logo: 2 Position</t>
+  </si>
+  <si>
+    <t>/uploads/1775539937170-1773913004907-WhatsApp_Image_2026-03-18_at_6_06_21___PM.jpeg</t>
+  </si>
+  <si>
+    <t>2026-04-26T08:57:44.378Z</t>
+  </si>
+  <si>
+    <t>b6e6c662-2a1d-42e2-9a82-bea7f5c49c38</t>
+  </si>
+  <si>
+    <t>GB-00004</t>
+  </si>
+  <si>
+    <t>HYUNDAI</t>
+  </si>
+  <si>
+    <t>Car Front Windshield Sunshade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product Name: Car Front Windshield Sunshade Size: 140×126×80 cm Material: Titanium Silver, Large: 372g Logo: 3 Position Remark: Start 2000 pcs 
+Product Name: Car Front Windshield Sunshade Size: 140×126×80 cm Material: Titanium Silver, Large: 372g Logo: 3 Position Remark: Start 2000 pcs</t>
+  </si>
+  <si>
+    <t>/uploads/1775540062550-1773915863014-PHOTO-2026-03-19-17-22-27.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T05:34:22.730Z</t>
+  </si>
+  <si>
+    <t>2026-04-21T06:04:59.594Z</t>
+  </si>
+  <si>
+    <t>f9287af2-17b1-4354-ad19-444a86149578</t>
+  </si>
+  <si>
+    <t>GB-00005</t>
+  </si>
+  <si>
+    <t>TMNPB</t>
+  </si>
+  <si>
+    <t>coffee cup plate set, shoes</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product Name: Caps and dish Size: 350 ml Material: ceramic Logo: 2 Position
+ Product Name: Caps Size: 380 ml Material: ceramic Logo: 1 Position
+Product Name: shoes Size: 23 ml Material: Plastic Logo: 1 Position</t>
+  </si>
+  <si>
+    <t>/uploads/1775540168063-1774610163459-PHOTO-2026-03-27-16-48-13.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T05:36:08.827Z</t>
+  </si>
+  <si>
+    <t>2026-04-13T02:10:55.176Z</t>
+  </si>
+  <si>
+    <t>173f619c-c3c1-48dd-b721-bc79299104bf</t>
+  </si>
+  <si>
+    <t>GB-00006</t>
+  </si>
+  <si>
+    <t>TOYOTA Lao Service</t>
+  </si>
+  <si>
+    <t>Shirt, Bottle, Umbrella, Pillow, cap</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product Name: Polo shirt Capacity: 550ml Material: Stainless Steel 304, art Logo: 1 Position 
+Product Name: Bottle Capacity: 550ml Material: Stainless Steel 304 Logo: 1 Position 
+Product Name: Umbrella (UV Coating), Automatic close Size: 21inches Ribs: 8 ribs Logo: 4 positions, full color printing Product Name: Umbrella (UV Coating), Automatic close Size: 21inches Ribs: 8 ribs Logo: 4 positions, full color printing 
+Product Name: Umbrella Doublelayer size: 30 inch Material: fiber glass , save UV Logo: 4 Position 
+Product Name: Car neck pillow Material: fabric Size : 19*26 cm printing: logo 1 point Product Name: caps Material: cotton Size : 54-62 printing: logo 1 point</t>
+  </si>
+  <si>
+    <t>/uploads/1775540283722-1775455056621-toyota-brand-logo-car-symbol-with-name-black-design-japan-automobi.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-26T08:56:46.659Z</t>
+  </si>
+  <si>
+    <t>26f84f50-b501-4145-b7e1-1f0e870cc920</t>
+  </si>
+  <si>
+    <t>GB-00007</t>
+  </si>
+  <si>
+    <t>MAISONNONGKHIAW</t>
+  </si>
+  <si>
+    <t>Mug</t>
+  </si>
+  <si>
+    <t>Product Name: Mug Material: ceramic size: 350ml logo: 2 point</t>
+  </si>
+  <si>
+    <t>/uploads/1775540377731-1775455299324-Unknown</t>
+  </si>
+  <si>
+    <t>2026-04-26T08:52:36.486Z</t>
+  </si>
+  <si>
+    <t>ce6f4cb5-7440-4872-b0b2-24395abbfeeb</t>
+  </si>
+  <si>
+    <t>GB-00008</t>
+  </si>
+  <si>
+    <t>Artsawin Sokxay</t>
+  </si>
+  <si>
+    <t>Bag, cup</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product Name: bags
+size: 40*30*10
+Material: canvar A12
+Logo: 2 Position
+Product Name: cup
+size: 450ml
+Material:stainless
+Logo: 2 Position</t>
+  </si>
+  <si>
+    <t>/uploads/1776070267191-PHOTO-2026-04-13-15-31-36.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-26T08:53:01.142Z</t>
   </si>
   <si>
     <t>projectId</t>
@@ -114,6 +308,630 @@
   </si>
   <si>
     <t>billPath</t>
+  </si>
+  <si>
+    <t>1abebbf3-d5b8-4774-b6b6-7ec92681373c</t>
+  </si>
+  <si>
+    <t>expense</t>
+  </si>
+  <si>
+    <t>Facebook Ad</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>/uploads/1775558588121-1773741352134-Screenshot_2026-03-17_at_4_51_03___PM.png</t>
+  </si>
+  <si>
+    <t>2026-04-07T10:43:08.852Z</t>
+  </si>
+  <si>
+    <t>b16b09ff-be48-45c7-8ca0-f621be79ad69</t>
+  </si>
+  <si>
+    <t>Rider</t>
+  </si>
+  <si>
+    <t>/uploads/1775558651144-1773740650605-WhatsApp_Image_2026-03-17_at_4_07_46_PM.jpeg</t>
+  </si>
+  <si>
+    <t>2026-04-07T10:44:11.511Z</t>
+  </si>
+  <si>
+    <t>df6ae782-4e3e-43c8-868c-68108ca0f8f0</t>
+  </si>
+  <si>
+    <t>Logistic</t>
+  </si>
+  <si>
+    <t>/uploads/1775558766672-1773814306098-WhatsApp_Image_2026-03-18_at_1_11_24_PM.jpeg</t>
+  </si>
+  <si>
+    <t>2026-04-07T10:46:07.020Z</t>
+  </si>
+  <si>
+    <t>b099cb18-8641-421b-a73d-03a09b3ad9b6</t>
+  </si>
+  <si>
+    <t>Logistics rider</t>
+  </si>
+  <si>
+    <t>/uploads/1775559178541-PHOTO-2026-03-19-16-37-39.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T10:52:59.071Z</t>
+  </si>
+  <si>
+    <t>88bb37bc-5c93-441b-8e1f-f80af3730ca1</t>
+  </si>
+  <si>
+    <t>Bag</t>
+  </si>
+  <si>
+    <t>/uploads/1775559351637-PHOTO-2026-03-19-16-59-55.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T10:55:51.813Z</t>
+  </si>
+  <si>
+    <t>67f00208-74c0-456a-93b4-db63a095ca4d</t>
+  </si>
+  <si>
+    <t>income</t>
+  </si>
+  <si>
+    <t>Tumbler</t>
+  </si>
+  <si>
+    <t>/uploads/1775559434520-PHOTO-2026-03-20-12-36-54.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T10:57:14.700Z</t>
+  </si>
+  <si>
+    <t>6e9fca66-0c93-4b5a-821c-86d7925e5357</t>
+  </si>
+  <si>
+    <t>RAILWAY Domain (5 USD)</t>
+  </si>
+  <si>
+    <t>/uploads/1775559503077-PHOTO-2026-03-21-12-23-07.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T10:58:23.428Z</t>
+  </si>
+  <si>
+    <t>bbd054cf-3068-4841-81f2-1f29f07f6899</t>
+  </si>
+  <si>
+    <t>investment</t>
+  </si>
+  <si>
+    <t>Order production</t>
+  </si>
+  <si>
+    <t>/uploads/1775559632455-PHOTO-2026-03-19-16-52-03.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:00:32.630Z</t>
+  </si>
+  <si>
+    <t>2dc7ed1d-6242-4abe-81f6-a21726ef9178</t>
+  </si>
+  <si>
+    <t>Document envelopes</t>
+  </si>
+  <si>
+    <t>/uploads/1775559702547-PHOTO-2026-03-19-17-02-52.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:01:42.731Z</t>
+  </si>
+  <si>
+    <t>d540c4d5-b996-4b7b-9966-74ae199c8f94</t>
+  </si>
+  <si>
+    <t>Example</t>
+  </si>
+  <si>
+    <t>/uploads/1775559770264-PHOTO-2026-03-19-17-11-45.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:02:50.838Z</t>
+  </si>
+  <si>
+    <t>9c5e0770-3075-4c3c-88d5-4817e7ba2fc3</t>
+  </si>
+  <si>
+    <t>/uploads/1775559888356-PHOTO-2026-03-19-18-42-47.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:04:48.530Z</t>
+  </si>
+  <si>
+    <t>9a0ab234-53b9-4c60-8e0a-d791656131ba</t>
+  </si>
+  <si>
+    <t>Notebook</t>
+  </si>
+  <si>
+    <t>/uploads/1775559961384-WhatsApp_Image_2026-03-19_at_6_43_03___PM__1_.jpeg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:06:01.925Z</t>
+  </si>
+  <si>
+    <t>4c623da0-d785-471a-9aa2-88dca0a4119f</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:06:42.514Z</t>
+  </si>
+  <si>
+    <t>e11f8d40-1a03-4fe4-a81d-1f7b3963fc64</t>
+  </si>
+  <si>
+    <t>Example of car front windshield</t>
+  </si>
+  <si>
+    <t>/uploads/1775560182245-PHOTO-2026-03-22-17-53-16.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:09:42.421Z</t>
+  </si>
+  <si>
+    <t>8bdb2281-c5b7-4f42-a57e-989b0ad3ce70</t>
+  </si>
+  <si>
+    <t>Advertising Services</t>
+  </si>
+  <si>
+    <t>/uploads/1775560246709-PHOTO-2026-03-23-09-57-16.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:10:46.877Z</t>
+  </si>
+  <si>
+    <t>83c3c232-d6d3-4581-9d9a-e89f159b61b3</t>
+  </si>
+  <si>
+    <t>/uploads/1775560298018-PHOTO-2026-03-24-13-09-12.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:11:38.379Z</t>
+  </si>
+  <si>
+    <t>dbc30f02-fbd2-4df5-812a-1f2c688ef02b</t>
+  </si>
+  <si>
+    <t>J-flag The Capital Plus</t>
+  </si>
+  <si>
+    <t>/uploads/1775560418581-PHOTO-2026-03-27-16-37-37.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:13:38.931Z</t>
+  </si>
+  <si>
+    <t>c0ec9a58-04af-4dbc-b8f0-4747a62dd77d</t>
+  </si>
+  <si>
+    <t>Deposit</t>
+  </si>
+  <si>
+    <t>Coffee cup 30%</t>
+  </si>
+  <si>
+    <t>/uploads/1775560515903-PHOTO-2026-03-27-16-47-15.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:15:16.644Z</t>
+  </si>
+  <si>
+    <t>82bb2c14-b210-40f2-8863-81b60c5cbf26</t>
+  </si>
+  <si>
+    <t>Coffee cup cup plate set, shoes 30%</t>
+  </si>
+  <si>
+    <t>/uploads/1775560693444-PHOTO-2026-03-27-16-49-15.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:18:14.156Z</t>
+  </si>
+  <si>
+    <t>816c63c5-983c-4f7c-aaed-34173360e3df</t>
+  </si>
+  <si>
+    <t>shoes 30%</t>
+  </si>
+  <si>
+    <t>/uploads/1775560828329-PHOTO-2026-03-27-16-50-06.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:20:29.030Z</t>
+  </si>
+  <si>
+    <t>b38a6a97-2e77-4ad0-b10b-1eef89a55bd2</t>
+  </si>
+  <si>
+    <t>Vongdeuan jewelry shop</t>
+  </si>
+  <si>
+    <t>/uploads/1775560922047-PHOTO-2026-03-28-12-04-41.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:22:02.636Z</t>
+  </si>
+  <si>
+    <t>9d27188e-924d-4244-9339-7327e51e06f9</t>
+  </si>
+  <si>
+    <t>Bonus for employees</t>
+  </si>
+  <si>
+    <t>/uploads/1775560968482-PHOTO-2026-03-28-13-02-42.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:22:48.850Z</t>
+  </si>
+  <si>
+    <t>83756289-0d05-4821-abe6-a63d2fc018bc</t>
+  </si>
+  <si>
+    <t>Advertising Services facebook</t>
+  </si>
+  <si>
+    <t>/uploads/1775561053124-PHOTO-2026-03-28-13-46-55.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:24:13.313Z</t>
+  </si>
+  <si>
+    <t>ca7fcb00-776e-4fd4-89d6-d7e66d134bf5</t>
+  </si>
+  <si>
+    <t>coffee cup plate set</t>
+  </si>
+  <si>
+    <t>/uploads/1775561160183-WhatsApp_Image_2026-03-31_at_1_30_23___PM__2_.jpeg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:26:00.970Z</t>
+  </si>
+  <si>
+    <t>03cec6e0-5375-40db-907e-0eb9528b23b3</t>
+  </si>
+  <si>
+    <t>/uploads/1775561206312-WhatsApp_Image_2026-03-31_at_1_30_23___PM__1_.jpeg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:26:47.470Z</t>
+  </si>
+  <si>
+    <t>27bda833-f1f4-4166-9a5c-f4bf41025672</t>
+  </si>
+  <si>
+    <t>Umbrella</t>
+  </si>
+  <si>
+    <t>/uploads/1775561261430-WhatsApp_Image_2026-04-01_at_4_30_04___PM.jpeg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:27:42.379Z</t>
+  </si>
+  <si>
+    <t>21942361-1cd7-4dc7-884a-b6872ebbf6a8</t>
+  </si>
+  <si>
+    <t>Example of cap</t>
+  </si>
+  <si>
+    <t>/uploads/1775561317975-PHOTO-2026-04-01-16-30-45.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:28:39.077Z</t>
+  </si>
+  <si>
+    <t>31ea2ba3-2fab-4711-9f3d-65ae108c8659</t>
+  </si>
+  <si>
+    <t>Employees allowance</t>
+  </si>
+  <si>
+    <t>/uploads/1775561369458-PHOTO-2026-04-02-12-44-40.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:29:30.656Z</t>
+  </si>
+  <si>
+    <t>6d0afb8a-d723-4b42-b5b1-b1fb115d3f49</t>
+  </si>
+  <si>
+    <t>/uploads/1775561414315-PHOTO-2026-04-03-10-21-39.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:30:15.013Z</t>
+  </si>
+  <si>
+    <t>ecabc4cb-49c9-494d-83ef-7ca754fe229f</t>
+  </si>
+  <si>
+    <t>Laser machine</t>
+  </si>
+  <si>
+    <t>/uploads/1775561510901-PHOTO-2026-04-04-09-09-46.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:31:51.260Z</t>
+  </si>
+  <si>
+    <t>29b35bb7-d3d1-434b-874e-47ab0350e2d5</t>
+  </si>
+  <si>
+    <t>/uploads/1775561629836-WhatsApp_Image_2026-04-05_at_10_02_47___AM__1_.jpeg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:33:50.377Z</t>
+  </si>
+  <si>
+    <t>36840310-7517-4dc2-855f-3577e1e122b8</t>
+  </si>
+  <si>
+    <t>/uploads/1775561800954-WhatsApp_Image_2026-04-05_at_10_02_48___AM__4_.jpeg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:36:41.509Z</t>
+  </si>
+  <si>
+    <t>5b65b417-20eb-4088-a208-d456f82c6c91</t>
+  </si>
+  <si>
+    <t>/uploads/1775561979473-WhatsApp_Image_2026-04-05_at_10_02_48___AM__1_.jpeg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:39:40.031Z</t>
+  </si>
+  <si>
+    <t>f1c89884-28d6-432a-a278-d3b50dd8d76e</t>
+  </si>
+  <si>
+    <t>/uploads/1775562044482-PHOTO-2026-04-06-09-19-52.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:40:44.658Z</t>
+  </si>
+  <si>
+    <t>d0748394-aaea-4dc0-88aa-07e404bb2905</t>
+  </si>
+  <si>
+    <t>Mini phone shipping costs</t>
+  </si>
+  <si>
+    <t>/uploads/1775562128348-WhatsApp_Image_2026-04-06_at_9_16_32___AM.jpeg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:42:09.309Z</t>
+  </si>
+  <si>
+    <t>3d6ec844-8ad5-427a-97c8-bfd1f1fe31e7</t>
+  </si>
+  <si>
+    <t>Vongduean jewelry shipping costs</t>
+  </si>
+  <si>
+    <t>/uploads/1775562315511-WhatsApp_Image_2026-04-06_at_9_16_33___AM__3_.jpeg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:45:16.510Z</t>
+  </si>
+  <si>
+    <t>33500c3d-0ec4-4682-8c84-59fa750ead4a</t>
+  </si>
+  <si>
+    <t>Tourism Malaysia shipping costs</t>
+  </si>
+  <si>
+    <t>/uploads/1775562397825-WhatsApp_Image_2026-04-06_at_9_16_33___AM__4_.jpeg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:46:38.538Z</t>
+  </si>
+  <si>
+    <t>5f5da9c6-a3d8-4f87-8999-cf429b0e4980</t>
+  </si>
+  <si>
+    <t>Laser machine shipping costs</t>
+  </si>
+  <si>
+    <t>/uploads/1775562505596-WhatsApp_Image_2026-04-06_at_9_16_33___AM__5_.jpeg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:48:27.655Z</t>
+  </si>
+  <si>
+    <t>66530a77-3fb4-4a98-b509-4813eb5ac150</t>
+  </si>
+  <si>
+    <t>Coffee cup</t>
+  </si>
+  <si>
+    <t>/uploads/1775562583316-PHOTO-2026-04-06-10-11-41.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:49:43.490Z</t>
+  </si>
+  <si>
+    <t>b1d78d47-e3f6-49f3-a6c5-da166b236687</t>
+  </si>
+  <si>
+    <t>Shipping costs</t>
+  </si>
+  <si>
+    <t>/uploads/1775562624493-PHOTO-2026-04-06-14-54-50.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T11:50:25.197Z</t>
+  </si>
+  <si>
+    <t>087873fe-e320-42e1-bf49-5e6c28dbca2c</t>
+  </si>
+  <si>
+    <t>/uploads/1775569197267-PHOTO-2026-04-07-12-52-44.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-07T13:39:57.445Z</t>
+  </si>
+  <si>
+    <t>1a3abde4-5f2a-410d-821b-66def2183934</t>
+  </si>
+  <si>
+    <t>Costs of sending cap example to China</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>/uploads/1775625573380-PHOTO-2026-04-07-19-05-20.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-08T05:19:34.128Z</t>
+  </si>
+  <si>
+    <t>d119d26e-0e3e-4417-aa51-4e1745d0a0c0</t>
+  </si>
+  <si>
+    <t>Railway domain (36.96 USD)</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>/uploads/1775881882915-PHOTO-2026-04-11-11-19-54.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-11T04:31:23.273Z</t>
+  </si>
+  <si>
+    <t>144939b5-dc78-4906-8704-e33a6dc5afff</t>
+  </si>
+  <si>
+    <t>shoes</t>
+  </si>
+  <si>
+    <t>/uploads/1776046251808-PHOTO-2026-04-13-08-25-39.jpg</t>
+  </si>
+  <si>
+    <t>3fb17b02-fff3-4fb4-a813-a5c66c5a5e6d</t>
+  </si>
+  <si>
+    <t>/uploads/1776046417632-PHOTO-2026-04-13-08-28-12.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-13T02:13:37.819Z</t>
+  </si>
+  <si>
+    <t>1f7b5c76-ddcf-4232-8901-bb3ab86699cf</t>
+  </si>
+  <si>
+    <t>/uploads/1776092317063-WhatsApp_Image_2026-04-13_at_4_34_31___PM__1_.jpeg</t>
+  </si>
+  <si>
+    <t>2026-04-13T14:58:37.618Z</t>
+  </si>
+  <si>
+    <t>9c97c9f3-8071-49a4-8395-2c643a8d23ba</t>
+  </si>
+  <si>
+    <t>Cup</t>
+  </si>
+  <si>
+    <t>/uploads/1776092373991-WhatsApp_Image_2026-04-13_at_4_34_31___PM.jpeg</t>
+  </si>
+  <si>
+    <t>2026-04-13T14:59:34.670Z</t>
+  </si>
+  <si>
+    <t>f3315315-2299-40d7-8035-1a0c09f1144f</t>
+  </si>
+  <si>
+    <t>/uploads/1776092436549-PHOTO-2026-04-13-17-05-34.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-13T15:00:36.739Z</t>
+  </si>
+  <si>
+    <t>befb5b19-eb24-42f1-bf42-1ccfea4d0e5e</t>
+  </si>
+  <si>
+    <t>Total payment</t>
+  </si>
+  <si>
+    <t>Grand total</t>
+  </si>
+  <si>
+    <t>2026-04-14</t>
+  </si>
+  <si>
+    <t>2026-04-14T04:34:46.043Z</t>
+  </si>
+  <si>
+    <t>d18ba81c-d52c-461c-be31-1092c03ee66a</t>
+  </si>
+  <si>
+    <t>Example of umbrella</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>/uploads/1776336941467-WhatsApp_Image_2026-04-16_at_4_02_43___PM__2_.jpeg</t>
+  </si>
+  <si>
+    <t>2026-04-16T10:55:42.023Z</t>
+  </si>
+  <si>
+    <t>9dc93aba-1297-4ef1-ba08-f5a1b72a7144</t>
+  </si>
+  <si>
+    <t>/uploads/1776336979474-WhatsApp_Image_2026-04-16_at_4_02_43___PM__3_.jpeg</t>
+  </si>
+  <si>
+    <t>2026-04-16T10:56:20.000Z</t>
+  </si>
+  <si>
+    <t>4e63ed44-060f-4ac1-88d7-e6ef9b7c0b01</t>
+  </si>
+  <si>
+    <t>Example of umbrella of Kia</t>
+  </si>
+  <si>
+    <t>/uploads/1776427063395-PHOTO-2026-04-17-18-28-03.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-17T11:57:43.936Z</t>
+  </si>
+  <si>
+    <t>e2405586-7c89-46ca-b8f9-afb9e617766f</t>
+  </si>
+  <si>
+    <t>/uploads/1776751499064-PHOTO-2026-04-21-08-32-52.jpg</t>
+  </si>
+  <si>
+    <t>7ac1ef54-bab2-4bb2-b921-7305999a8057</t>
+  </si>
+  <si>
+    <t>Advertising services Facebook</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>/uploads/1777179165232-PHOTO-2026-04-26-11-17-21.jpg</t>
+  </si>
+  <si>
+    <t>2026-04-26T04:52:45.407Z</t>
   </si>
 </sst>
 </file>
@@ -502,13 +1320,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="8.83203125"/>
   <cols>
-    <col min="1" max="15" width="22" customWidth="1"/>
+    <col min="1" max="17" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -554,37 +1372,43 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -593,13 +1417,372 @@
         <v>0</v>
       </c>
       <c r="M2">
+        <v>-59983999</v>
+      </c>
+      <c r="N2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3">
+        <v>18700000</v>
+      </c>
+      <c r="M3">
+        <v>10</v>
+      </c>
+      <c r="N3">
+        <v>20570000</v>
+      </c>
+      <c r="O3">
+        <v>-9671836</v>
+      </c>
+      <c r="P3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4">
+        <v>28600000</v>
+      </c>
+      <c r="M4">
+        <v>10</v>
+      </c>
+      <c r="N4">
+        <v>31460000</v>
+      </c>
+      <c r="O4">
+        <v>13874460</v>
+      </c>
+      <c r="P4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" t="s">
+        <v>51</v>
+      </c>
+      <c r="K5">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>-31595076</v>
+      </c>
+      <c r="N5" t="s">
+        <v>52</v>
+      </c>
+      <c r="O5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" t="s">
         <v>24</v>
       </c>
-      <c r="O2" t="s">
-        <v>25</v>
+      <c r="H6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" t="s">
+        <v>60</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>-20092260</v>
+      </c>
+      <c r="N6" t="s">
+        <v>61</v>
+      </c>
+      <c r="O6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" t="s">
+        <v>68</v>
+      </c>
+      <c r="J7" t="s">
+        <v>69</v>
+      </c>
+      <c r="K7" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7">
+        <v>1062512000</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
+      </c>
+      <c r="N7">
+        <v>1168763200</v>
+      </c>
+      <c r="O7">
+        <v>1166795200</v>
+      </c>
+      <c r="P7" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" t="s">
+        <v>75</v>
+      </c>
+      <c r="J8" t="s">
+        <v>76</v>
+      </c>
+      <c r="K8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8">
+        <v>7700000</v>
+      </c>
+      <c r="M8">
+        <v>10</v>
+      </c>
+      <c r="N8">
+        <v>8470000</v>
+      </c>
+      <c r="O8">
+        <v>5146330</v>
+      </c>
+      <c r="P8" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J9" t="s">
+        <v>84</v>
+      </c>
+      <c r="K9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9">
+        <v>9790000</v>
+      </c>
+      <c r="M9">
+        <v>10</v>
+      </c>
+      <c r="N9">
+        <v>10769000</v>
+      </c>
+      <c r="O9">
+        <v>2466000</v>
+      </c>
+      <c r="P9" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -610,7 +1793,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="8.83203125"/>
   <cols>
     <col min="1" max="12" width="22" customWidth="1"/>
@@ -624,34 +1807,2086 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2">
+        <v>983000</v>
+      </c>
+      <c r="I2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3">
+        <v>60000</v>
+      </c>
+      <c r="I3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4">
+        <v>34000</v>
+      </c>
+      <c r="I4" t="s">
+        <v>96</v>
+      </c>
+      <c r="J4" t="s">
+        <v>105</v>
+      </c>
+      <c r="K4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5">
+        <v>50000</v>
+      </c>
+      <c r="I5" t="s">
+        <v>96</v>
+      </c>
+      <c r="J5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K5" t="s">
+        <v>110</v>
+      </c>
+      <c r="L5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>112</v>
+      </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6">
+        <v>4489700</v>
+      </c>
+      <c r="I6" t="s">
+        <v>96</v>
+      </c>
+      <c r="J6" t="s">
+        <v>113</v>
+      </c>
+      <c r="K6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7">
+        <v>5250000</v>
+      </c>
+      <c r="I7" t="s">
+        <v>96</v>
+      </c>
+      <c r="J7" t="s">
+        <v>118</v>
+      </c>
+      <c r="K7" t="s">
+        <v>119</v>
+      </c>
+      <c r="L7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" t="s">
+        <v>121</v>
+      </c>
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8">
+        <v>108040</v>
+      </c>
+      <c r="I8" t="s">
+        <v>96</v>
+      </c>
+      <c r="J8" t="s">
+        <v>122</v>
+      </c>
+      <c r="K8" t="s">
+        <v>123</v>
+      </c>
+      <c r="L8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="D9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F9" t="s">
+        <v>112</v>
+      </c>
+      <c r="G9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9">
+        <v>5204176</v>
+      </c>
+      <c r="I9" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" t="s">
+        <v>127</v>
+      </c>
+      <c r="K9" t="s">
+        <v>128</v>
+      </c>
+      <c r="L9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>125</v>
+      </c>
+      <c r="E10" t="s">
+        <v>126</v>
+      </c>
+      <c r="F10" t="s">
+        <v>130</v>
+      </c>
+      <c r="G10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10">
+        <v>4657660</v>
+      </c>
+      <c r="I10" t="s">
+        <v>96</v>
+      </c>
+      <c r="J10" t="s">
+        <v>131</v>
+      </c>
+      <c r="K10" t="s">
+        <v>132</v>
+      </c>
+      <c r="L10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F11" t="s">
+        <v>134</v>
+      </c>
+      <c r="G11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11">
+        <v>969000</v>
+      </c>
+      <c r="I11" t="s">
+        <v>96</v>
+      </c>
+      <c r="J11" t="s">
+        <v>135</v>
+      </c>
+      <c r="K11" t="s">
+        <v>136</v>
+      </c>
+      <c r="L11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" t="s">
+        <v>125</v>
+      </c>
+      <c r="E12" t="s">
+        <v>126</v>
+      </c>
+      <c r="F12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12">
+        <v>9496200</v>
+      </c>
+      <c r="I12" t="s">
+        <v>96</v>
+      </c>
+      <c r="J12" t="s">
+        <v>138</v>
+      </c>
+      <c r="K12" t="s">
+        <v>139</v>
+      </c>
+      <c r="L12" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>140</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E13" t="s">
+        <v>126</v>
+      </c>
+      <c r="F13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13">
+        <v>6460000</v>
+      </c>
+      <c r="I13" t="s">
+        <v>96</v>
+      </c>
+      <c r="J13" t="s">
+        <v>142</v>
+      </c>
+      <c r="K13" t="s">
+        <v>143</v>
+      </c>
+      <c r="L13" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>144</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" t="s">
+        <v>125</v>
+      </c>
+      <c r="E14" t="s">
+        <v>126</v>
+      </c>
+      <c r="F14" t="s">
+        <v>141</v>
+      </c>
+      <c r="G14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14">
+        <v>187340</v>
+      </c>
+      <c r="I14" t="s">
+        <v>96</v>
+      </c>
+      <c r="J14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" t="s">
+        <v>145</v>
+      </c>
+      <c r="L14" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>146</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" t="s">
+        <v>147</v>
+      </c>
+      <c r="G15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15">
+        <v>32300</v>
+      </c>
+      <c r="I15" t="s">
+        <v>96</v>
+      </c>
+      <c r="J15" t="s">
+        <v>148</v>
+      </c>
+      <c r="K15" t="s">
+        <v>149</v>
+      </c>
+      <c r="L15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>150</v>
+      </c>
+      <c r="B16">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" t="s">
+        <v>151</v>
+      </c>
+      <c r="G16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16">
+        <v>591864</v>
+      </c>
+      <c r="I16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J16" t="s">
+        <v>152</v>
+      </c>
+      <c r="K16" t="s">
+        <v>153</v>
+      </c>
+      <c r="L16" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>154</v>
+      </c>
+      <c r="B17">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" t="s">
+        <v>104</v>
+      </c>
+      <c r="G17" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17">
+        <v>75000</v>
+      </c>
+      <c r="I17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J17" t="s">
+        <v>155</v>
+      </c>
+      <c r="K17" t="s">
+        <v>156</v>
+      </c>
+      <c r="L17" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>157</v>
+      </c>
+      <c r="B18">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" t="s">
+        <v>158</v>
+      </c>
+      <c r="G18" t="s">
+        <v>35</v>
+      </c>
+      <c r="H18">
+        <v>1296000</v>
+      </c>
+      <c r="I18" t="s">
+        <v>96</v>
+      </c>
+      <c r="J18" t="s">
+        <v>159</v>
+      </c>
+      <c r="K18" t="s">
+        <v>160</v>
+      </c>
+      <c r="L18" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>161</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E19" t="s">
+        <v>162</v>
+      </c>
+      <c r="F19" t="s">
+        <v>163</v>
+      </c>
+      <c r="G19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H19">
+        <v>1889000</v>
+      </c>
+      <c r="I19" t="s">
+        <v>96</v>
+      </c>
+      <c r="J19" t="s">
+        <v>164</v>
+      </c>
+      <c r="K19" t="s">
+        <v>165</v>
+      </c>
+      <c r="L19" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>166</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" t="s">
+        <v>116</v>
+      </c>
+      <c r="E20" t="s">
+        <v>162</v>
+      </c>
+      <c r="F20" t="s">
+        <v>167</v>
+      </c>
+      <c r="G20" t="s">
+        <v>35</v>
+      </c>
+      <c r="H20">
+        <v>8490000</v>
+      </c>
+      <c r="I20" t="s">
+        <v>96</v>
+      </c>
+      <c r="J20" t="s">
+        <v>168</v>
+      </c>
+      <c r="K20" t="s">
+        <v>169</v>
+      </c>
+      <c r="L20" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>170</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" t="s">
+        <v>125</v>
+      </c>
+      <c r="E21" t="s">
+        <v>126</v>
+      </c>
+      <c r="F21" t="s">
+        <v>171</v>
+      </c>
+      <c r="G21" t="s">
+        <v>35</v>
+      </c>
+      <c r="H21">
+        <v>1312000</v>
+      </c>
+      <c r="I21" t="s">
+        <v>96</v>
+      </c>
+      <c r="J21" t="s">
+        <v>172</v>
+      </c>
+      <c r="K21" t="s">
+        <v>173</v>
+      </c>
+      <c r="L21" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>174</v>
+      </c>
+      <c r="B22">
+        <v>11</v>
+      </c>
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" t="s">
+        <v>116</v>
+      </c>
+      <c r="E22" t="s">
+        <v>112</v>
+      </c>
+      <c r="F22" t="s">
+        <v>175</v>
+      </c>
+      <c r="G22" t="s">
+        <v>35</v>
+      </c>
+      <c r="H22">
+        <v>29756000</v>
+      </c>
+      <c r="I22" t="s">
+        <v>96</v>
+      </c>
+      <c r="J22" t="s">
+        <v>176</v>
+      </c>
+      <c r="K22" t="s">
+        <v>177</v>
+      </c>
+      <c r="L22" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>178</v>
+      </c>
+      <c r="B23">
+        <v>12</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" t="s">
+        <v>179</v>
+      </c>
+      <c r="G23" t="s">
+        <v>35</v>
+      </c>
+      <c r="H23">
+        <v>32396000</v>
+      </c>
+      <c r="I23" t="s">
+        <v>96</v>
+      </c>
+      <c r="J23" t="s">
+        <v>180</v>
+      </c>
+      <c r="K23" t="s">
+        <v>181</v>
+      </c>
+      <c r="L23" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>182</v>
+      </c>
+      <c r="B24">
+        <v>13</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" t="s">
+        <v>183</v>
+      </c>
+      <c r="G24" t="s">
+        <v>35</v>
+      </c>
+      <c r="H24">
+        <v>750150</v>
+      </c>
+      <c r="I24" t="s">
+        <v>96</v>
+      </c>
+      <c r="J24" t="s">
+        <v>184</v>
+      </c>
+      <c r="K24" t="s">
+        <v>185</v>
+      </c>
+      <c r="L24" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>186</v>
+      </c>
+      <c r="B25">
+        <v>4</v>
+      </c>
+      <c r="C25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" t="s">
+        <v>125</v>
+      </c>
+      <c r="E25" t="s">
+        <v>126</v>
+      </c>
+      <c r="F25" t="s">
+        <v>187</v>
+      </c>
+      <c r="G25" t="s">
+        <v>35</v>
+      </c>
+      <c r="H25">
+        <v>9925000</v>
+      </c>
+      <c r="I25" t="s">
+        <v>96</v>
+      </c>
+      <c r="J25" t="s">
+        <v>188</v>
+      </c>
+      <c r="K25" t="s">
+        <v>189</v>
+      </c>
+      <c r="L25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>190</v>
+      </c>
+      <c r="B26">
+        <v>5</v>
+      </c>
+      <c r="C26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" t="s">
+        <v>125</v>
+      </c>
+      <c r="E26" t="s">
+        <v>126</v>
+      </c>
+      <c r="F26" t="s">
+        <v>187</v>
+      </c>
+      <c r="G26" t="s">
+        <v>35</v>
+      </c>
+      <c r="H26">
+        <v>790000</v>
+      </c>
+      <c r="I26" t="s">
+        <v>96</v>
+      </c>
+      <c r="J26" t="s">
+        <v>191</v>
+      </c>
+      <c r="K26" t="s">
+        <v>192</v>
+      </c>
+      <c r="L26" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>193</v>
+      </c>
+      <c r="B27">
+        <v>3</v>
+      </c>
+      <c r="C27" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" t="s">
+        <v>125</v>
+      </c>
+      <c r="E27" t="s">
+        <v>126</v>
+      </c>
+      <c r="F27" t="s">
+        <v>194</v>
+      </c>
+      <c r="G27" t="s">
+        <v>35</v>
+      </c>
+      <c r="H27">
+        <v>7672000</v>
+      </c>
+      <c r="I27" t="s">
+        <v>96</v>
+      </c>
+      <c r="J27" t="s">
+        <v>195</v>
+      </c>
+      <c r="K27" t="s">
+        <v>196</v>
+      </c>
+      <c r="L27" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>197</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" t="s">
+        <v>20</v>
+      </c>
+      <c r="F28" t="s">
+        <v>198</v>
+      </c>
+      <c r="G28" t="s">
+        <v>35</v>
+      </c>
+      <c r="H28">
+        <v>264000</v>
+      </c>
+      <c r="I28" t="s">
+        <v>96</v>
+      </c>
+      <c r="J28" t="s">
+        <v>199</v>
+      </c>
+      <c r="K28" t="s">
+        <v>200</v>
+      </c>
+      <c r="L28" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>201</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" t="s">
+        <v>94</v>
+      </c>
+      <c r="E29" t="s">
+        <v>20</v>
+      </c>
+      <c r="F29" t="s">
+        <v>202</v>
+      </c>
+      <c r="G29" t="s">
+        <v>35</v>
+      </c>
+      <c r="H29">
+        <v>1168000</v>
+      </c>
+      <c r="I29" t="s">
+        <v>96</v>
+      </c>
+      <c r="J29" t="s">
+        <v>203</v>
+      </c>
+      <c r="K29" t="s">
+        <v>204</v>
+      </c>
+      <c r="L29" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>205</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" t="s">
+        <v>125</v>
+      </c>
+      <c r="E30" t="s">
+        <v>126</v>
+      </c>
+      <c r="F30" t="s">
+        <v>49</v>
+      </c>
+      <c r="G30" t="s">
+        <v>35</v>
+      </c>
+      <c r="H30">
+        <v>25157000</v>
+      </c>
+      <c r="I30" t="s">
+        <v>96</v>
+      </c>
+      <c r="J30" t="s">
+        <v>206</v>
+      </c>
+      <c r="K30" t="s">
+        <v>207</v>
+      </c>
+      <c r="L30" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>208</v>
+      </c>
+      <c r="B31">
+        <v>14</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" t="s">
+        <v>94</v>
+      </c>
+      <c r="E31" t="s">
+        <v>20</v>
+      </c>
+      <c r="F31" t="s">
+        <v>209</v>
+      </c>
+      <c r="G31" t="s">
+        <v>35</v>
+      </c>
+      <c r="H31">
+        <v>11470620</v>
+      </c>
+      <c r="I31" t="s">
+        <v>96</v>
+      </c>
+      <c r="J31" t="s">
+        <v>210</v>
+      </c>
+      <c r="K31" t="s">
+        <v>211</v>
+      </c>
+      <c r="L31" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>212</v>
+      </c>
+      <c r="B32">
+        <v>4</v>
+      </c>
+      <c r="C32" t="s">
+        <v>28</v>
+      </c>
+      <c r="D32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E32" t="s">
+        <v>126</v>
+      </c>
+      <c r="F32" t="s">
+        <v>130</v>
+      </c>
+      <c r="G32" t="s">
+        <v>35</v>
+      </c>
+      <c r="H32">
+        <v>7036000</v>
+      </c>
+      <c r="I32" t="s">
+        <v>96</v>
+      </c>
+      <c r="J32" t="s">
+        <v>213</v>
+      </c>
+      <c r="K32" t="s">
+        <v>214</v>
+      </c>
+      <c r="L32" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>215</v>
+      </c>
+      <c r="B33">
+        <v>5</v>
+      </c>
+      <c r="C33" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E33" t="s">
+        <v>126</v>
+      </c>
+      <c r="F33" t="s">
+        <v>130</v>
+      </c>
+      <c r="G33" t="s">
+        <v>35</v>
+      </c>
+      <c r="H33">
+        <v>5592000</v>
+      </c>
+      <c r="I33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J33" t="s">
+        <v>216</v>
+      </c>
+      <c r="K33" t="s">
+        <v>217</v>
+      </c>
+      <c r="L33" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>218</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" t="s">
+        <v>125</v>
+      </c>
+      <c r="E34" t="s">
+        <v>134</v>
+      </c>
+      <c r="F34" t="s">
+        <v>198</v>
+      </c>
+      <c r="G34" t="s">
+        <v>35</v>
+      </c>
+      <c r="H34">
+        <v>1968000</v>
+      </c>
+      <c r="I34" t="s">
+        <v>96</v>
+      </c>
+      <c r="J34" t="s">
+        <v>219</v>
+      </c>
+      <c r="K34" t="s">
+        <v>220</v>
+      </c>
+      <c r="L34" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>221</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" t="s">
+        <v>116</v>
+      </c>
+      <c r="E35" t="s">
+        <v>162</v>
+      </c>
+      <c r="F35" t="s">
+        <v>74</v>
+      </c>
+      <c r="G35" t="s">
+        <v>35</v>
+      </c>
+      <c r="H35">
+        <v>2000000</v>
+      </c>
+      <c r="I35" t="s">
+        <v>96</v>
+      </c>
+      <c r="J35" t="s">
+        <v>222</v>
+      </c>
+      <c r="K35" t="s">
+        <v>223</v>
+      </c>
+      <c r="L35" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>224</v>
+      </c>
+      <c r="B36">
+        <v>15</v>
+      </c>
+      <c r="C36" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" t="s">
+        <v>94</v>
+      </c>
+      <c r="E36" t="s">
+        <v>20</v>
+      </c>
+      <c r="F36" t="s">
+        <v>225</v>
+      </c>
+      <c r="G36" t="s">
+        <v>35</v>
+      </c>
+      <c r="H36">
+        <v>410000</v>
+      </c>
+      <c r="I36" t="s">
+        <v>96</v>
+      </c>
+      <c r="J36" t="s">
+        <v>226</v>
+      </c>
+      <c r="K36" t="s">
+        <v>227</v>
+      </c>
+      <c r="L36" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>228</v>
+      </c>
+      <c r="B37">
+        <v>16</v>
+      </c>
+      <c r="C37" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" t="s">
+        <v>94</v>
+      </c>
+      <c r="E37" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37" t="s">
+        <v>229</v>
+      </c>
+      <c r="G37" t="s">
+        <v>35</v>
+      </c>
+      <c r="H37">
+        <v>940000</v>
+      </c>
+      <c r="I37" t="s">
+        <v>96</v>
+      </c>
+      <c r="J37" t="s">
+        <v>230</v>
+      </c>
+      <c r="K37" t="s">
+        <v>231</v>
+      </c>
+      <c r="L37" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>232</v>
+      </c>
+      <c r="B38">
+        <v>4</v>
+      </c>
+      <c r="C38" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" t="s">
+        <v>94</v>
+      </c>
+      <c r="E38" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" t="s">
+        <v>233</v>
+      </c>
+      <c r="G38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H38">
+        <v>1442000</v>
+      </c>
+      <c r="I38" t="s">
+        <v>96</v>
+      </c>
+      <c r="J38" t="s">
+        <v>234</v>
+      </c>
+      <c r="K38" t="s">
+        <v>235</v>
+      </c>
+      <c r="L38" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>236</v>
+      </c>
+      <c r="B39">
+        <v>17</v>
+      </c>
+      <c r="C39" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" t="s">
+        <v>94</v>
+      </c>
+      <c r="E39" t="s">
+        <v>20</v>
+      </c>
+      <c r="F39" t="s">
+        <v>237</v>
+      </c>
+      <c r="G39" t="s">
+        <v>35</v>
+      </c>
+      <c r="H39">
+        <v>137000</v>
+      </c>
+      <c r="I39" t="s">
+        <v>96</v>
+      </c>
+      <c r="J39" t="s">
+        <v>238</v>
+      </c>
+      <c r="K39" t="s">
+        <v>239</v>
+      </c>
+      <c r="L39" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>240</v>
+      </c>
+      <c r="B40">
+        <v>6</v>
+      </c>
+      <c r="C40" t="s">
+        <v>54</v>
+      </c>
+      <c r="D40" t="s">
+        <v>125</v>
+      </c>
+      <c r="E40" t="s">
+        <v>126</v>
+      </c>
+      <c r="F40" t="s">
+        <v>241</v>
+      </c>
+      <c r="G40" t="s">
+        <v>35</v>
+      </c>
+      <c r="H40">
+        <v>1815260</v>
+      </c>
+      <c r="I40" t="s">
+        <v>96</v>
+      </c>
+      <c r="J40" t="s">
+        <v>242</v>
+      </c>
+      <c r="K40" t="s">
+        <v>243</v>
+      </c>
+      <c r="L40" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>244</v>
+      </c>
+      <c r="B41">
+        <v>6</v>
+      </c>
+      <c r="C41" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" t="s">
+        <v>94</v>
+      </c>
+      <c r="E41" t="s">
+        <v>20</v>
+      </c>
+      <c r="F41" t="s">
+        <v>245</v>
+      </c>
+      <c r="G41" t="s">
+        <v>35</v>
+      </c>
+      <c r="H41">
+        <v>80000</v>
+      </c>
+      <c r="I41" t="s">
+        <v>96</v>
+      </c>
+      <c r="J41" t="s">
+        <v>246</v>
+      </c>
+      <c r="K41" t="s">
+        <v>247</v>
+      </c>
+      <c r="L41" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>248</v>
+      </c>
+      <c r="B42">
+        <v>18</v>
+      </c>
+      <c r="C42" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" t="s">
+        <v>94</v>
+      </c>
+      <c r="E42" t="s">
+        <v>20</v>
+      </c>
+      <c r="F42" t="s">
+        <v>183</v>
+      </c>
+      <c r="G42" t="s">
+        <v>35</v>
+      </c>
+      <c r="H42">
+        <v>759375</v>
+      </c>
+      <c r="I42" t="s">
+        <v>96</v>
+      </c>
+      <c r="J42" t="s">
+        <v>249</v>
+      </c>
+      <c r="K42" t="s">
+        <v>250</v>
+      </c>
+      <c r="L42" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>251</v>
+      </c>
+      <c r="B43">
+        <v>19</v>
+      </c>
+      <c r="C43" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" t="s">
+        <v>94</v>
+      </c>
+      <c r="E43" t="s">
+        <v>20</v>
+      </c>
+      <c r="F43" t="s">
+        <v>252</v>
+      </c>
+      <c r="G43" t="s">
+        <v>35</v>
+      </c>
+      <c r="H43">
+        <v>3100000</v>
+      </c>
+      <c r="I43" t="s">
+        <v>253</v>
+      </c>
+      <c r="J43" t="s">
+        <v>254</v>
+      </c>
+      <c r="K43" t="s">
+        <v>255</v>
+      </c>
+      <c r="L43" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>256</v>
+      </c>
+      <c r="B44">
+        <v>20</v>
+      </c>
+      <c r="C44" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" t="s">
+        <v>94</v>
+      </c>
+      <c r="E44" t="s">
+        <v>20</v>
+      </c>
+      <c r="F44" t="s">
+        <v>257</v>
+      </c>
+      <c r="G44" t="s">
+        <v>35</v>
+      </c>
+      <c r="H44">
+        <v>831600</v>
+      </c>
+      <c r="I44" t="s">
+        <v>258</v>
+      </c>
+      <c r="J44" t="s">
+        <v>259</v>
+      </c>
+      <c r="K44" t="s">
+        <v>260</v>
+      </c>
+      <c r="L44" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>261</v>
+      </c>
+      <c r="B45">
+        <v>7</v>
+      </c>
+      <c r="C45" t="s">
+        <v>54</v>
+      </c>
+      <c r="D45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E45" t="s">
+        <v>126</v>
+      </c>
+      <c r="F45" t="s">
+        <v>262</v>
+      </c>
+      <c r="G45" t="s">
+        <v>35</v>
+      </c>
+      <c r="H45">
+        <v>4361000</v>
+      </c>
+      <c r="I45" t="s">
+        <v>42</v>
+      </c>
+      <c r="J45" t="s">
+        <v>263</v>
+      </c>
+      <c r="K45" t="s">
+        <v>62</v>
+      </c>
+      <c r="L45" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>264</v>
+      </c>
+      <c r="B46">
+        <v>2</v>
+      </c>
+      <c r="C46" t="s">
+        <v>71</v>
+      </c>
+      <c r="D46" t="s">
+        <v>125</v>
+      </c>
+      <c r="E46" t="s">
+        <v>126</v>
+      </c>
+      <c r="F46" t="s">
+        <v>74</v>
+      </c>
+      <c r="G46" t="s">
+        <v>35</v>
+      </c>
+      <c r="H46">
+        <v>3323670</v>
+      </c>
+      <c r="I46" t="s">
+        <v>42</v>
+      </c>
+      <c r="J46" t="s">
+        <v>265</v>
+      </c>
+      <c r="K46" t="s">
+        <v>266</v>
+      </c>
+      <c r="L46" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>267</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>78</v>
+      </c>
+      <c r="D47" t="s">
+        <v>125</v>
+      </c>
+      <c r="E47" t="s">
+        <v>126</v>
+      </c>
+      <c r="F47" t="s">
+        <v>112</v>
+      </c>
+      <c r="G47" t="s">
+        <v>35</v>
+      </c>
+      <c r="H47">
+        <v>5281000</v>
+      </c>
+      <c r="I47" t="s">
+        <v>42</v>
+      </c>
+      <c r="J47" t="s">
+        <v>268</v>
+      </c>
+      <c r="K47" t="s">
+        <v>269</v>
+      </c>
+      <c r="L47" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>270</v>
+      </c>
+      <c r="B48">
+        <v>2</v>
+      </c>
+      <c r="C48" t="s">
+        <v>78</v>
+      </c>
+      <c r="D48" t="s">
+        <v>125</v>
+      </c>
+      <c r="E48" t="s">
+        <v>126</v>
+      </c>
+      <c r="F48" t="s">
+        <v>271</v>
+      </c>
+      <c r="G48" t="s">
+        <v>35</v>
+      </c>
+      <c r="H48">
+        <v>3022000</v>
+      </c>
+      <c r="I48" t="s">
+        <v>42</v>
+      </c>
+      <c r="J48" t="s">
+        <v>272</v>
+      </c>
+      <c r="K48" t="s">
+        <v>273</v>
+      </c>
+      <c r="L48" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>274</v>
+      </c>
+      <c r="B49">
+        <v>21</v>
+      </c>
+      <c r="C49" t="s">
+        <v>17</v>
+      </c>
+      <c r="D49" t="s">
+        <v>94</v>
+      </c>
+      <c r="E49" t="s">
+        <v>20</v>
+      </c>
+      <c r="F49" t="s">
+        <v>183</v>
+      </c>
+      <c r="G49" t="s">
+        <v>35</v>
+      </c>
+      <c r="H49">
+        <v>757800</v>
+      </c>
+      <c r="I49" t="s">
+        <v>42</v>
+      </c>
+      <c r="J49" t="s">
+        <v>275</v>
+      </c>
+      <c r="K49" t="s">
+        <v>276</v>
+      </c>
+      <c r="L49" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>277</v>
+      </c>
+      <c r="B50">
+        <v>5</v>
+      </c>
+      <c r="C50" t="s">
+        <v>37</v>
+      </c>
+      <c r="D50" t="s">
+        <v>116</v>
+      </c>
+      <c r="E50" t="s">
+        <v>278</v>
+      </c>
+      <c r="F50" t="s">
+        <v>279</v>
+      </c>
+      <c r="G50" t="s">
+        <v>35</v>
+      </c>
+      <c r="H50">
+        <v>28160000</v>
+      </c>
+      <c r="I50" t="s">
+        <v>280</v>
+      </c>
+      <c r="J50" t="s">
+        <v>24</v>
+      </c>
+      <c r="K50" t="s">
+        <v>281</v>
+      </c>
+      <c r="L50" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>282</v>
+      </c>
+      <c r="B51">
+        <v>6</v>
+      </c>
+      <c r="C51" t="s">
+        <v>46</v>
+      </c>
+      <c r="D51" t="s">
+        <v>125</v>
+      </c>
+      <c r="E51" t="s">
+        <v>134</v>
+      </c>
+      <c r="F51" t="s">
+        <v>283</v>
+      </c>
+      <c r="G51" t="s">
+        <v>35</v>
+      </c>
+      <c r="H51">
+        <v>1000563</v>
+      </c>
+      <c r="I51" t="s">
+        <v>284</v>
+      </c>
+      <c r="J51" t="s">
+        <v>285</v>
+      </c>
+      <c r="K51" t="s">
+        <v>286</v>
+      </c>
+      <c r="L51" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>287</v>
+      </c>
+      <c r="B52">
+        <v>7</v>
+      </c>
+      <c r="C52" t="s">
+        <v>46</v>
+      </c>
+      <c r="D52" t="s">
+        <v>125</v>
+      </c>
+      <c r="E52" t="s">
+        <v>126</v>
+      </c>
+      <c r="F52" t="s">
+        <v>74</v>
+      </c>
+      <c r="G52" t="s">
+        <v>35</v>
+      </c>
+      <c r="H52">
+        <v>2334647</v>
+      </c>
+      <c r="I52" t="s">
+        <v>284</v>
+      </c>
+      <c r="J52" t="s">
+        <v>288</v>
+      </c>
+      <c r="K52" t="s">
+        <v>289</v>
+      </c>
+      <c r="L52" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>290</v>
+      </c>
+      <c r="B53">
+        <v>8</v>
+      </c>
+      <c r="C53" t="s">
+        <v>46</v>
+      </c>
+      <c r="D53" t="s">
+        <v>94</v>
+      </c>
+      <c r="E53" t="s">
+        <v>20</v>
+      </c>
+      <c r="F53" t="s">
+        <v>291</v>
+      </c>
+      <c r="G53" t="s">
+        <v>35</v>
+      </c>
+      <c r="H53">
+        <v>334665</v>
+      </c>
+      <c r="I53" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>14</v>
+      <c r="J53" t="s">
+        <v>292</v>
+      </c>
+      <c r="K53" t="s">
+        <v>293</v>
+      </c>
+      <c r="L53" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>294</v>
+      </c>
+      <c r="B54">
+        <v>9</v>
+      </c>
+      <c r="C54" t="s">
+        <v>46</v>
+      </c>
+      <c r="D54" t="s">
+        <v>94</v>
+      </c>
+      <c r="E54" t="s">
+        <v>20</v>
+      </c>
+      <c r="F54" t="s">
+        <v>291</v>
+      </c>
+      <c r="G54" t="s">
+        <v>35</v>
+      </c>
+      <c r="H54">
+        <v>334901</v>
+      </c>
+      <c r="I54" t="s">
+        <v>58</v>
+      </c>
+      <c r="J54" t="s">
+        <v>295</v>
+      </c>
+      <c r="K54" t="s">
+        <v>53</v>
+      </c>
+      <c r="L54" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>296</v>
+      </c>
+      <c r="B55">
+        <v>22</v>
+      </c>
+      <c r="C55" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55" t="s">
+        <v>94</v>
+      </c>
+      <c r="E55" t="s">
+        <v>20</v>
+      </c>
+      <c r="F55" t="s">
+        <v>297</v>
+      </c>
+      <c r="G55" t="s">
+        <v>35</v>
+      </c>
+      <c r="H55">
+        <v>743850</v>
+      </c>
+      <c r="I55" t="s">
+        <v>298</v>
+      </c>
+      <c r="J55" t="s">
+        <v>299</v>
+      </c>
+      <c r="K55" t="s">
+        <v>300</v>
+      </c>
+      <c r="L55" t="s">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
